--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.31902412465305</v>
+        <v>11.26434142025612</v>
       </c>
       <c r="D2" t="n">
-        <v>53.41582162618113</v>
+        <v>8.680071014254434</v>
       </c>
       <c r="E2" t="n">
-        <v>21.62555987030322</v>
+        <v>3.514153478924274</v>
       </c>
       <c r="F2" t="n">
-        <v>15.28021057163187</v>
+        <v>2.483034217890179</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.57403414594076</v>
+        <v>8.543280548715375</v>
       </c>
       <c r="D3" t="n">
-        <v>7.826237921249264</v>
+        <v>1.271763662203006</v>
       </c>
       <c r="E3" t="n">
-        <v>21.62555987030322</v>
+        <v>3.514153478924274</v>
       </c>
       <c r="F3" t="n">
-        <v>15.28021057163187</v>
+        <v>2.483034217890179</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.0201665710421</v>
+        <v>5.203277067794341</v>
       </c>
       <c r="D4" t="n">
-        <v>19.52562418976663</v>
+        <v>3.172913930837078</v>
       </c>
       <c r="E4" t="n">
-        <v>21.62555987030322</v>
+        <v>3.514153478924274</v>
       </c>
       <c r="F4" t="n">
-        <v>15.28021057163187</v>
+        <v>2.483034217890179</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.69650647650151</v>
+        <v>4.338182302431496</v>
       </c>
       <c r="D5" t="n">
-        <v>13.64734406395618</v>
+        <v>2.217693410392879</v>
       </c>
       <c r="E5" t="n">
-        <v>21.62555987030322</v>
+        <v>3.514153478924274</v>
       </c>
       <c r="F5" t="n">
-        <v>15.28021057163187</v>
+        <v>2.483034217890179</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.24935067318552</v>
+        <v>3.940519484392648</v>
       </c>
       <c r="D6" t="n">
-        <v>16.47782139065724</v>
+        <v>2.677645975981802</v>
       </c>
       <c r="E6" t="n">
-        <v>21.62555987030322</v>
+        <v>3.514153478924274</v>
       </c>
       <c r="F6" t="n">
-        <v>15.28021057163187</v>
+        <v>2.483034217890179</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1.410380209589212</v>
+        <v>0.2291867840582469</v>
       </c>
       <c r="D7" t="n">
-        <v>10.85592633393693</v>
+        <v>1.764088029264751</v>
       </c>
       <c r="E7" t="n">
-        <v>21.62555987030322</v>
+        <v>3.514153478924274</v>
       </c>
       <c r="F7" t="n">
-        <v>15.28021057163187</v>
+        <v>2.483034217890179</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
